--- a/jogos_2024-09-23.xlsx
+++ b/jogos_2024-09-23.xlsx
@@ -643,23 +643,23 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
         <v>1</v>
       </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
@@ -669,83 +669,83 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="M2" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N2" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="O2" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="P2" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="R2" t="n">
         <v>1.38</v>
       </c>
       <c r="S2" t="n">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="T2" t="n">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="U2" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="V2" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W2" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="X2" t="n">
-        <v>3.14</v>
+        <v>3.4</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
+          <t>['38', '82']</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>['82']</t>
-        </is>
-      </c>
       <c r="AG2" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="AK2" s="3" t="n">
         <v>45558.22916666666</v>
@@ -772,22 +772,22 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -798,83 +798,83 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="M3" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N3" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="O3" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="P3" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="R3" t="n">
         <v>1.38</v>
       </c>
       <c r="S3" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="T3" t="n">
-        <v>2.7</v>
+        <v>2.77</v>
       </c>
       <c r="U3" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="V3" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X3" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>['82']</t>
+        </is>
+      </c>
+      <c r="AG3" t="n">
         <v>1.28</v>
       </c>
-      <c r="X3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>['38', '82']</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AH3" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AJ3" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45558.22916666666</v>
@@ -1288,19 +1288,19 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Sloboda Užice</t>
         </is>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
@@ -1314,49 +1314,49 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.6</v>
+        <v>1.85</v>
       </c>
       <c r="M7" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="N7" t="n">
-        <v>2</v>
+        <v>3.9</v>
       </c>
       <c r="O7" t="n">
-        <v>5</v>
+        <v>2.63</v>
       </c>
       <c r="P7" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.75</v>
+        <v>4.75</v>
       </c>
       <c r="R7" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="S7" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="T7" t="n">
-        <v>3.6</v>
+        <v>3.56</v>
       </c>
       <c r="U7" t="n">
         <v>1.25</v>
       </c>
       <c r="V7" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="W7" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="X7" t="n">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.75</v>
+        <v>2.42</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AA7" t="n">
         <v>5.5</v>
@@ -1365,32 +1365,32 @@
         <v>1.11</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>['37']</t>
+          <t>['10']</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>['73']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.57</v>
+        <v>1.17</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.22</v>
+        <v>1.74</v>
       </c>
       <c r="AI7" t="n">
-        <v>3.2</v>
+        <v>1.62</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.62</v>
+        <v>3.1</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45558.45833333334</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,109 +1417,109 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
       </c>
       <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
         <v>1</v>
       </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.5</v>
+        <v>2.62</v>
       </c>
       <c r="M8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="O8" t="n">
         <v>3.5</v>
       </c>
-      <c r="N8" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O8" t="n">
-        <v>2.1</v>
-      </c>
       <c r="P8" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>7.5</v>
+        <v>3.1</v>
       </c>
       <c r="R8" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="S8" t="n">
-        <v>2.32</v>
+        <v>2.63</v>
       </c>
       <c r="T8" t="n">
-        <v>3.56</v>
+        <v>3.25</v>
       </c>
       <c r="U8" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="V8" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="W8" t="n">
-        <v>1.48</v>
+        <v>1.32</v>
       </c>
       <c r="X8" t="n">
-        <v>2.37</v>
+        <v>2.78</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.48</v>
+        <v>1.67</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.5</v>
+        <v>3.64</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.6</v>
+        <v>1.91</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.43</v>
+        <v>1.8</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>['31']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>['59']</t>
+          <t>['5']</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.04</v>
+        <v>1.45</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.38</v>
+        <v>1.35</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.36</v>
+        <v>2.25</v>
       </c>
       <c r="AJ8" t="n">
-        <v>4.75</v>
+        <v>1.8</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45558.45833333334</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,25 +1546,25 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
         <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1572,83 +1572,83 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.62</v>
+        <v>1.5</v>
       </c>
       <c r="M9" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="N9" t="n">
-        <v>2.24</v>
+        <v>6.5</v>
       </c>
       <c r="O9" t="n">
-        <v>3.5</v>
+        <v>2.1</v>
       </c>
       <c r="P9" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.1</v>
+        <v>7.5</v>
       </c>
       <c r="R9" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="S9" t="n">
-        <v>2.63</v>
+        <v>2.32</v>
       </c>
       <c r="T9" t="n">
-        <v>3.25</v>
+        <v>3.56</v>
       </c>
       <c r="U9" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="V9" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="W9" t="n">
-        <v>1.32</v>
+        <v>1.48</v>
       </c>
       <c r="X9" t="n">
-        <v>2.78</v>
+        <v>2.37</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.67</v>
+        <v>1.48</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.64</v>
+        <v>5.5</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.91</v>
+        <v>2.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.8</v>
+        <v>1.43</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['31']</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>['5']</t>
+          <t>['59']</t>
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.45</v>
+        <v>1.04</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.35</v>
+        <v>2.38</v>
       </c>
       <c r="AI9" t="n">
-        <v>2.25</v>
+        <v>1.36</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.8</v>
+        <v>4.75</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45558.45833333334</v>
@@ -1804,19 +1804,19 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sloboda Užice</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G11" t="n">
         <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
         <v>1</v>
@@ -1830,49 +1830,49 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.85</v>
+        <v>3.6</v>
       </c>
       <c r="M11" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="N11" t="n">
-        <v>3.9</v>
+        <v>2</v>
       </c>
       <c r="O11" t="n">
-        <v>2.63</v>
+        <v>5</v>
       </c>
       <c r="P11" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.75</v>
+        <v>2.75</v>
       </c>
       <c r="R11" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="S11" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="T11" t="n">
-        <v>3.56</v>
+        <v>3.6</v>
       </c>
       <c r="U11" t="n">
         <v>1.25</v>
       </c>
       <c r="V11" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="W11" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="X11" t="n">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.42</v>
+        <v>2.75</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AA11" t="n">
         <v>5.5</v>
@@ -1881,32 +1881,32 @@
         <v>1.11</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>['10']</t>
+          <t>['37']</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['73']</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.17</v>
+        <v>1.57</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.74</v>
+        <v>1.22</v>
       </c>
       <c r="AI11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AJ11" t="n">
         <v>1.62</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>3.1</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45558.45833333334</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,22 +2062,22 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Shakhtar Donetsk</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Radnički Sr. Mitrovica</t>
+          <t>Obolon-Brovar</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -2088,83 +2088,83 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.67</v>
+        <v>1.1</v>
       </c>
       <c r="M13" t="n">
-        <v>3.1</v>
+        <v>8</v>
       </c>
       <c r="N13" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="O13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>11</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T13" t="n">
         <v>2.25</v>
       </c>
-      <c r="P13" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="R13" t="n">
+      <c r="U13" t="n">
         <v>1.57</v>
       </c>
-      <c r="S13" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T13" t="n">
-        <v>4</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.2</v>
-      </c>
       <c r="V13" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="W13" t="n">
-        <v>1.57</v>
+        <v>1.13</v>
       </c>
       <c r="X13" t="n">
-        <v>2.15</v>
+        <v>4.3</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.68</v>
+        <v>1.55</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.39</v>
+        <v>2.3</v>
       </c>
       <c r="AA13" t="n">
-        <v>6.5</v>
+        <v>2.29</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.08</v>
+        <v>1.47</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
+          <t>['17', '67', '78', '90']</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG13" t="n">
-        <v>1.13</v>
+        <v>1.02</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.85</v>
+        <v>4.4</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.4</v>
+        <v>1.19</v>
       </c>
       <c r="AJ13" t="n">
-        <v>4.75</v>
+        <v>4.85</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45558.5</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,22 +2320,22 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Shakhtar Donetsk</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Obolon-Brovar</t>
+          <t>Mladost Novi Sad</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2346,83 +2346,83 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.1</v>
+        <v>3.5</v>
       </c>
       <c r="M15" t="n">
-        <v>8</v>
+        <v>3.1</v>
       </c>
       <c r="N15" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="O15" t="n">
-        <v>1.53</v>
+        <v>4.33</v>
       </c>
       <c r="P15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q15" t="n">
         <v>2.75</v>
       </c>
-      <c r="Q15" t="n">
-        <v>11</v>
-      </c>
       <c r="R15" t="n">
-        <v>1.29</v>
+        <v>1.56</v>
       </c>
       <c r="S15" t="n">
-        <v>3.5</v>
+        <v>2.31</v>
       </c>
       <c r="T15" t="n">
-        <v>2.25</v>
+        <v>3.42</v>
       </c>
       <c r="U15" t="n">
-        <v>1.57</v>
+        <v>1.27</v>
       </c>
       <c r="V15" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="W15" t="n">
-        <v>1.13</v>
+        <v>1.44</v>
       </c>
       <c r="X15" t="n">
-        <v>4.3</v>
+        <v>2.6</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.55</v>
+        <v>2.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.29</v>
+        <v>4.8</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.47</v>
+        <v>1.14</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.5</v>
+        <v>2.12</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>['17', '67', '78', '90']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['53']</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.02</v>
+        <v>1.6</v>
       </c>
       <c r="AH15" t="n">
-        <v>4.4</v>
+        <v>1.23</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.19</v>
+        <v>2.75</v>
       </c>
       <c r="AJ15" t="n">
-        <v>4.85</v>
+        <v>1.67</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45558.5</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,22 +2449,22 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Radnički Sr. Mitrovica</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2475,65 +2475,65 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="M16" t="n">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="N16" t="n">
+        <v>5</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q16" t="n">
         <v>7.5</v>
       </c>
-      <c r="O16" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>4.5</v>
-      </c>
       <c r="R16" t="n">
-        <v>1.3</v>
+        <v>1.57</v>
       </c>
       <c r="S16" t="n">
-        <v>3.4</v>
+        <v>2.25</v>
       </c>
       <c r="T16" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="U16" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="V16" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="W16" t="n">
-        <v>1.17</v>
+        <v>1.57</v>
       </c>
       <c r="X16" t="n">
-        <v>4.5</v>
+        <v>2.15</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.65</v>
+        <v>2.68</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.1</v>
+        <v>1.39</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.3</v>
+        <v>6.5</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.55</v>
+        <v>1.08</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.73</v>
+        <v>2.75</v>
       </c>
       <c r="AD16" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>['8']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -2542,16 +2542,16 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AJ16" t="n">
-        <v>2.88</v>
+        <v>4.75</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45558.5</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,23 +2578,23 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mladost Novi Sad</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
         <v>1</v>
       </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
@@ -2604,83 +2604,83 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.5</v>
+        <v>1.33</v>
       </c>
       <c r="M17" t="n">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="N17" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD17" t="n">
         <v>2</v>
       </c>
-      <c r="O17" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W17" t="n">
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>['8']</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AI17" t="n">
         <v>1.44</v>
       </c>
-      <c r="X17" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>['53']</t>
-        </is>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>2.75</v>
-      </c>
       <c r="AJ17" t="n">
-        <v>1.67</v>
+        <v>2.88</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45558.5</v>
@@ -3094,25 +3094,25 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G21" t="n">
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -3120,83 +3120,83 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="M21" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="N21" t="n">
-        <v>2.9</v>
+        <v>4.1</v>
       </c>
       <c r="O21" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="P21" t="n">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="R21" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="S21" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="T21" t="n">
-        <v>2.63</v>
+        <v>2.2</v>
       </c>
       <c r="U21" t="n">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="V21" t="n">
         <v>1.02</v>
       </c>
       <c r="W21" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X21" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>['65']</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
         <v>1.22</v>
       </c>
-      <c r="X21" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>['33']</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>['29', '73']</t>
-        </is>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH21" t="n">
-        <v>1.78</v>
+        <v>2.05</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.8</v>
+        <v>1.44</v>
       </c>
       <c r="AJ21" t="n">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45558.54166666666</v>
@@ -3223,25 +3223,25 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G22" t="n">
         <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I22" t="n">
         <v>1</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -3249,83 +3249,83 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="M22" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="N22" t="n">
-        <v>4.2</v>
+        <v>2.9</v>
       </c>
       <c r="O22" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X22" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>['33']</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>['29', '73']</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ22" t="n">
         <v>2.38</v>
-      </c>
-      <c r="P22" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>5</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T22" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X22" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>['35']</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>3.1</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45558.54166666666</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3367,7 +3367,7 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -3378,65 +3378,65 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="M23" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N23" t="n">
         <v>4.2</v>
       </c>
-      <c r="N23" t="n">
-        <v>4.1</v>
-      </c>
       <c r="O23" t="n">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="P23" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="R23" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="S23" t="n">
-        <v>3.75</v>
+        <v>2.5</v>
       </c>
       <c r="T23" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X23" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC23" t="n">
         <v>2.2</v>
       </c>
-      <c r="U23" t="n">
+      <c r="AD23" t="n">
         <v>1.62</v>
       </c>
-      <c r="V23" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X23" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>['65']</t>
+          <t>['35']</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -3445,16 +3445,16 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.05</v>
+        <v>1.74</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AJ23" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45558.54166666666</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,109 +3610,109 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
       </c>
       <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="M25" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N25" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O25" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P25" t="n">
         <v>2</v>
       </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L25" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="M25" t="n">
+      <c r="Q25" t="n">
         <v>3.5</v>
       </c>
-      <c r="N25" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="O25" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="P25" t="n">
+      <c r="R25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X25" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>['59']</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ25" t="n">
         <v>2.2</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X25" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>['13', '45+3', '90+4']</t>
-        </is>
-      </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>2.45</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45558.58333333334</v>
@@ -3729,22 +3729,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Gazişehir Gaziantep</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.05</v>
+        <v>2.35</v>
       </c>
       <c r="M26" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="N26" t="n">
-        <v>2.17</v>
+        <v>2.75</v>
       </c>
       <c r="O26" t="n">
-        <v>3.97</v>
+        <v>3.2</v>
       </c>
       <c r="P26" t="n">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.76</v>
+        <v>3.4</v>
       </c>
       <c r="R26" t="n">
         <v>1.38</v>
       </c>
       <c r="S26" t="n">
-        <v>3.08</v>
+        <v>2.85</v>
       </c>
       <c r="T26" t="n">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="U26" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="V26" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="W26" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="X26" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,16 +3832,16 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.7</v>
+        <v>1.47</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="AI26" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.77</v>
+        <v>1.97</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45558.58333333334</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,23 +3868,23 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>AaB</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G27" t="n">
+        <v>3</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
         <v>2</v>
       </c>
-      <c r="H27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0</v>
-      </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
@@ -3894,65 +3894,65 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.29</v>
+        <v>1.9</v>
       </c>
       <c r="M27" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="N27" t="n">
-        <v>10</v>
+        <v>3.75</v>
       </c>
       <c r="O27" t="n">
-        <v>1.67</v>
+        <v>2.3</v>
       </c>
       <c r="P27" t="n">
-        <v>2.88</v>
+        <v>2.2</v>
       </c>
       <c r="Q27" t="n">
-        <v>7.5</v>
+        <v>4.4</v>
       </c>
       <c r="R27" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="S27" t="n">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="T27" t="n">
-        <v>2</v>
+        <v>2.75</v>
       </c>
       <c r="U27" t="n">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="V27" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W27" t="n">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="X27" t="n">
-        <v>5.45</v>
+        <v>3.6</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.44</v>
+        <v>1.88</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.7</v>
+        <v>1.84</v>
       </c>
       <c r="AA27" t="n">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.73</v>
+        <v>1.3</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AD27" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>['63', '72']</t>
+          <t>['13', '45+3', '90+4']</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
@@ -3961,16 +3961,16 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="AH27" t="n">
-        <v>3.3</v>
+        <v>1.9</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.22</v>
+        <v>1.62</v>
       </c>
       <c r="AJ27" t="n">
-        <v>4.33</v>
+        <v>2.45</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45558.58333333334</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,19 +3997,19 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -4023,83 +4023,83 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.35</v>
+        <v>3.15</v>
       </c>
       <c r="M28" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="N28" t="n">
+        <v>2</v>
+      </c>
+      <c r="O28" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q28" t="n">
         <v>2.75</v>
       </c>
-      <c r="O28" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P28" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>3.4</v>
-      </c>
       <c r="R28" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="S28" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="T28" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="U28" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="V28" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="W28" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="X28" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AA28" t="n">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AD28" t="n">
         <v>2.05</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['79']</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['80']</t>
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.47</v>
+        <v>1.73</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.9</v>
+        <v>2.38</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1.97</v>
+        <v>1.67</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45558.58333333334</v>
@@ -4116,29 +4116,29 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Gazişehir Gaziantep</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -4152,83 +4152,83 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.5</v>
+        <v>3.05</v>
       </c>
       <c r="M29" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="N29" t="n">
-        <v>5.5</v>
+        <v>2.17</v>
       </c>
       <c r="O29" t="n">
-        <v>2.1</v>
+        <v>3.97</v>
       </c>
       <c r="P29" t="n">
-        <v>2.38</v>
+        <v>2.26</v>
       </c>
       <c r="Q29" t="n">
-        <v>5.5</v>
+        <v>2.76</v>
       </c>
       <c r="R29" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="S29" t="n">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="T29" t="n">
-        <v>2.63</v>
+        <v>2.86</v>
       </c>
       <c r="U29" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="V29" t="n">
         <v>1.03</v>
       </c>
       <c r="W29" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="X29" t="n">
-        <v>3.74</v>
+        <v>3.6</v>
       </c>
       <c r="Y29" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG29" t="n">
         <v>1.7</v>
       </c>
-      <c r="Z29" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>['89']</t>
-        </is>
-      </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>['78']</t>
-        </is>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AH29" t="n">
-        <v>2.43</v>
+        <v>1.25</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="AJ29" t="n">
-        <v>3.2</v>
+        <v>1.77</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45558.58333333334</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,22 +4255,22 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -4281,83 +4281,83 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.97</v>
+        <v>2.3</v>
       </c>
       <c r="M30" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="N30" t="n">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="O30" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="P30" t="n">
         <v>2.05</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="R30" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="S30" t="n">
-        <v>2.6</v>
+        <v>2.89</v>
       </c>
       <c r="T30" t="n">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="U30" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="V30" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="W30" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="X30" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="Y30" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Z30" t="n">
         <v>1.75</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>['28']</t>
+          <t>['24', '29']</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>['81']</t>
+          <t>['52', '90+4']</t>
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.55</v>
+        <v>1.43</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AJ30" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45558.58333333334</v>
@@ -4503,29 +4503,29 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -4539,83 +4539,83 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.55</v>
+        <v>4.5</v>
       </c>
       <c r="M32" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="N32" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="O32" t="n">
-        <v>3.4</v>
+        <v>4.75</v>
       </c>
       <c r="P32" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z32" t="n">
         <v>2</v>
       </c>
-      <c r="Q32" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S32" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="X32" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AA32" t="n">
-        <v>3.72</v>
+        <v>2.8</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.91</v>
+        <v>1.72</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>['59']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['58', '90']</t>
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.45</v>
+        <v>1.93</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.47</v>
+        <v>1.16</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.91</v>
+        <v>2.62</v>
       </c>
       <c r="AJ32" t="n">
-        <v>2.2</v>
+        <v>1.53</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45558.58333333334</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,83 +4668,83 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.15</v>
+        <v>1.5</v>
       </c>
       <c r="M33" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="N33" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="O33" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P33" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X33" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z33" t="n">
         <v>2</v>
       </c>
-      <c r="O33" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="P33" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S33" t="n">
-        <v>3</v>
-      </c>
-      <c r="T33" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X33" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AA33" t="n">
-        <v>2.88</v>
+        <v>2.65</v>
       </c>
       <c r="AB33" t="n">
         <v>1.36</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>['79']</t>
+          <t>['89']</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>['80']</t>
+          <t>['78']</t>
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.73</v>
+        <v>1.14</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.33</v>
+        <v>2.43</v>
       </c>
       <c r="AI33" t="n">
-        <v>2.38</v>
+        <v>1.4</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1.67</v>
+        <v>3.2</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45558.58333333334</v>
@@ -4761,119 +4761,119 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>AaB</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="M34" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="N34" t="n">
+        <v>10</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="P34" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S34" t="n">
+        <v>4</v>
+      </c>
+      <c r="T34" t="n">
         <v>2</v>
       </c>
-      <c r="I34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L34" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="M34" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="N34" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="O34" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="P34" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S34" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T34" t="n">
-        <v>2.5</v>
-      </c>
       <c r="U34" t="n">
-        <v>1.47</v>
+        <v>1.73</v>
       </c>
       <c r="V34" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W34" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X34" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>['63', '72']</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG34" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AI34" t="n">
         <v>1.22</v>
       </c>
-      <c r="X34" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF34" t="inlineStr">
-        <is>
-          <t>['58', '90']</t>
-        </is>
-      </c>
-      <c r="AG34" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>2.62</v>
-      </c>
       <c r="AJ34" t="n">
-        <v>1.53</v>
+        <v>4.33</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45558.58333333334</v>
@@ -4890,119 +4890,119 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>4</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
         <v>2</v>
       </c>
-      <c r="H35" t="n">
-        <v>2</v>
-      </c>
-      <c r="I35" t="n">
-        <v>2</v>
-      </c>
-      <c r="J35" t="n">
-        <v>0</v>
-      </c>
       <c r="K35" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L35" t="n">
+        <v>5</v>
+      </c>
+      <c r="M35" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="N35" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="O35" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="P35" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q35" t="n">
         <v>2.3</v>
-      </c>
-      <c r="M35" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N35" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="O35" t="n">
-        <v>3</v>
-      </c>
-      <c r="P35" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>3.4</v>
       </c>
       <c r="R35" t="n">
         <v>1.36</v>
       </c>
       <c r="S35" t="n">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="T35" t="n">
-        <v>2.72</v>
+        <v>2.63</v>
       </c>
       <c r="U35" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="V35" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W35" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="X35" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="Y35" t="n">
-        <v>2.05</v>
+        <v>1.55</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="AA35" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>['24', '29']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>['52', '90+4']</t>
+          <t>['24', '45+3', '55', '65']</t>
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.39</v>
+        <v>1.91</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.43</v>
+        <v>1.2</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.8</v>
+        <v>2.75</v>
       </c>
       <c r="AJ35" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45558.58333333334</v>
@@ -5019,119 +5019,119 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H36" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="M36" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N36" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O36" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P36" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S36" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X36" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Y36" t="n">
         <v>2</v>
       </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L36" t="n">
-        <v>5</v>
-      </c>
-      <c r="M36" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="N36" t="n">
+      <c r="Z36" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>['28']</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>['81']</t>
+        </is>
+      </c>
+      <c r="AG36" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH36" t="n">
         <v>1.55</v>
       </c>
-      <c r="O36" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="P36" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="R36" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S36" t="n">
-        <v>3</v>
-      </c>
-      <c r="T36" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U36" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V36" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X36" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF36" t="inlineStr">
-        <is>
-          <t>['24', '45+3', '55', '65']</t>
-        </is>
-      </c>
-      <c r="AG36" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AI36" t="n">
-        <v>2.75</v>
+        <v>1.73</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="AK36" s="3" t="n">
         <v>45558.58333333334</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,22 +5416,22 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
         <v>1</v>
@@ -5442,83 +5442,83 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="M39" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N39" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="O39" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="P39" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S39" t="n">
         <v>3.4</v>
       </c>
-      <c r="N39" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="O39" t="n">
-        <v>4.68</v>
-      </c>
-      <c r="P39" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S39" t="n">
-        <v>2.82</v>
-      </c>
       <c r="T39" t="n">
-        <v>3.07</v>
+        <v>2.38</v>
       </c>
       <c r="U39" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="V39" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W39" t="n">
-        <v>1.27</v>
+        <v>1.15</v>
       </c>
       <c r="X39" t="n">
-        <v>3.04</v>
+        <v>4.6</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.88</v>
+        <v>1.62</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.88</v>
+        <v>2.25</v>
       </c>
       <c r="AA39" t="n">
-        <v>3.34</v>
+        <v>2.5</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.22</v>
+        <v>1.45</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.86</v>
+        <v>1.57</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.84</v>
+        <v>2.25</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
-          <t>['31']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>['24', '60']</t>
+          <t>['30', '53', '72', '82']</t>
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AH39" t="n">
         <v>1.22</v>
       </c>
       <c r="AI39" t="n">
-        <v>2.66</v>
+        <v>2.38</v>
       </c>
       <c r="AJ39" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AK39" s="3" t="n">
         <v>45558.625</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,25 +5674,25 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Ma'an</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -5700,83 +5700,83 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.45</v>
+        <v>1.27</v>
       </c>
       <c r="M41" t="n">
-        <v>3.6</v>
+        <v>4.75</v>
       </c>
       <c r="N41" t="n">
-        <v>2.45</v>
+        <v>9.5</v>
       </c>
       <c r="O41" t="n">
-        <v>2.88</v>
+        <v>1.73</v>
       </c>
       <c r="P41" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.88</v>
+        <v>9.5</v>
       </c>
       <c r="R41" t="n">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="S41" t="n">
-        <v>4</v>
+        <v>2.63</v>
       </c>
       <c r="T41" t="n">
-        <v>2.1</v>
+        <v>3.25</v>
       </c>
       <c r="U41" t="n">
-        <v>1.67</v>
+        <v>1.33</v>
       </c>
       <c r="V41" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W41" t="n">
-        <v>1.08</v>
+        <v>1.36</v>
       </c>
       <c r="X41" t="n">
-        <v>6.5</v>
+        <v>3.1</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.4</v>
+        <v>1.95</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.88</v>
+        <v>1.85</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.9</v>
+        <v>4.33</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.78</v>
+        <v>1.2</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.36</v>
+        <v>2.63</v>
       </c>
       <c r="AD41" t="n">
-        <v>3</v>
+        <v>1.44</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
-          <t>['70', '72']</t>
+          <t>['41']</t>
         </is>
       </c>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>['41', '82']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.55</v>
+        <v>1.02</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.49</v>
+        <v>3.08</v>
       </c>
       <c r="AI41" t="n">
-        <v>1.83</v>
+        <v>1.2</v>
       </c>
       <c r="AJ41" t="n">
-        <v>1.83</v>
+        <v>6</v>
       </c>
       <c r="AK41" s="3" t="n">
         <v>45558.625</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,22 +5803,22 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H42" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
         <v>1</v>
@@ -5829,83 +5829,83 @@
         </is>
       </c>
       <c r="L42" t="n">
+        <v>4</v>
+      </c>
+      <c r="M42" t="n">
         <v>3.4</v>
       </c>
-      <c r="M42" t="n">
-        <v>3.5</v>
-      </c>
       <c r="N42" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="O42" t="n">
-        <v>3.75</v>
+        <v>4.68</v>
       </c>
       <c r="P42" t="n">
-        <v>2.38</v>
+        <v>2.18</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="R42" t="n">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="S42" t="n">
-        <v>3.4</v>
+        <v>2.82</v>
       </c>
       <c r="T42" t="n">
-        <v>2.38</v>
+        <v>3.07</v>
       </c>
       <c r="U42" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="V42" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W42" t="n">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="X42" t="n">
-        <v>4.6</v>
+        <v>3.04</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.62</v>
+        <v>1.88</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.25</v>
+        <v>1.88</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.5</v>
+        <v>3.34</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.45</v>
+        <v>1.22</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.57</v>
+        <v>1.86</v>
       </c>
       <c r="AD42" t="n">
-        <v>2.25</v>
+        <v>1.84</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['31']</t>
         </is>
       </c>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>['30', '53', '72', '82']</t>
+          <t>['24', '60']</t>
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AH42" t="n">
         <v>1.22</v>
       </c>
       <c r="AI42" t="n">
-        <v>2.38</v>
+        <v>2.66</v>
       </c>
       <c r="AJ42" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AK42" s="3" t="n">
         <v>45558.625</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,109 +5932,109 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ma'an</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G43" t="n">
+        <v>2</v>
+      </c>
+      <c r="H43" t="n">
+        <v>2</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
         <v>1</v>
       </c>
-      <c r="H43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" t="n">
-        <v>1</v>
-      </c>
-      <c r="J43" t="n">
-        <v>0</v>
-      </c>
       <c r="K43" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.27</v>
+        <v>2.45</v>
       </c>
       <c r="M43" t="n">
-        <v>4.75</v>
+        <v>3.6</v>
       </c>
       <c r="N43" t="n">
-        <v>9.5</v>
+        <v>2.45</v>
       </c>
       <c r="O43" t="n">
-        <v>1.73</v>
+        <v>2.88</v>
       </c>
       <c r="P43" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="Q43" t="n">
-        <v>9.5</v>
+        <v>2.88</v>
       </c>
       <c r="R43" t="n">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="S43" t="n">
-        <v>2.63</v>
+        <v>4</v>
       </c>
       <c r="T43" t="n">
-        <v>3.25</v>
+        <v>2.1</v>
       </c>
       <c r="U43" t="n">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="V43" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W43" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X43" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AC43" t="n">
         <v>1.36</v>
       </c>
-      <c r="X43" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>2.63</v>
-      </c>
       <c r="AD43" t="n">
-        <v>1.44</v>
+        <v>3</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
-          <t>['41']</t>
+          <t>['70', '72']</t>
         </is>
       </c>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['41', '82']</t>
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.02</v>
+        <v>1.55</v>
       </c>
       <c r="AH43" t="n">
-        <v>3.08</v>
+        <v>1.49</v>
       </c>
       <c r="AI43" t="n">
-        <v>1.2</v>
+        <v>1.83</v>
       </c>
       <c r="AJ43" t="n">
-        <v>6</v>
+        <v>1.83</v>
       </c>
       <c r="AK43" s="3" t="n">
         <v>45558.625</v>
@@ -6438,26 +6438,26 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Milan II</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
@@ -6474,83 +6474,83 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="M47" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="N47" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="O47" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="P47" t="n">
         <v>2.1</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="R47" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="S47" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="T47" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="U47" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V47" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W47" t="n">
         <v>1.3</v>
       </c>
-      <c r="V47" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W47" t="n">
-        <v>1.33</v>
-      </c>
       <c r="X47" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="Y47" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AA47" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AC47" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>['58']</t>
+        </is>
+      </c>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG47" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AI47" t="n">
         <v>1.95</v>
       </c>
-      <c r="AD47" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG47" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AH47" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI47" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AJ47" t="n">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="AK47" s="3" t="n">
         <v>45558.65625</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,22 +6706,22 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -6732,65 +6732,65 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="M49" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="N49" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="O49" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="P49" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q49" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R49" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S49" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T49" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V49" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W49" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X49" t="n">
         <v>3</v>
       </c>
-      <c r="R49" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S49" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="T49" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="U49" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V49" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W49" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X49" t="n">
-        <v>3.14</v>
-      </c>
       <c r="Y49" t="n">
-        <v>1.88</v>
+        <v>2.1</v>
       </c>
       <c r="Z49" t="n">
-        <v>1.98</v>
+        <v>1.7</v>
       </c>
       <c r="AA49" t="n">
-        <v>3.08</v>
+        <v>4</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AC49" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.98</v>
+        <v>1.8</v>
       </c>
       <c r="AE49" t="inlineStr">
         <is>
-          <t>['39']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF49" t="inlineStr">
@@ -6799,16 +6799,16 @@
         </is>
       </c>
       <c r="AG49" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="AI49" t="n">
-        <v>2.06</v>
+        <v>2.3</v>
       </c>
       <c r="AJ49" t="n">
-        <v>1.96</v>
+        <v>1.73</v>
       </c>
       <c r="AK49" s="3" t="n">
         <v>45558.65625</v>
@@ -6825,32 +6825,32 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>SPAL</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -6861,28 +6861,28 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="M50" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="N50" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="O50" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P50" t="n">
         <v>2.3</v>
       </c>
-      <c r="P50" t="n">
-        <v>2.1</v>
-      </c>
       <c r="Q50" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="R50" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S50" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="T50" t="n">
         <v>3</v>
@@ -6891,53 +6891,53 @@
         <v>1.36</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Y50" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z50" t="n">
         <v>2</v>
       </c>
-      <c r="Z50" t="n">
+      <c r="AA50" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC50" t="n">
         <v>1.8</v>
       </c>
-      <c r="AA50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AD50" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AE50" t="inlineStr">
         <is>
-          <t>['38', '43']</t>
+          <t>['84']</t>
         </is>
       </c>
       <c r="AF50" t="inlineStr">
         <is>
-          <t>['60']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG50" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH50" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI50" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AJ50" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AK50" s="3" t="n">
         <v>45558.65625</v>
@@ -6964,22 +6964,22 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>SPAL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Milan II</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G51" t="n">
+        <v>2</v>
+      </c>
+      <c r="H51" t="n">
         <v>1</v>
       </c>
-      <c r="H51" t="n">
-        <v>0</v>
-      </c>
       <c r="I51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -6990,22 +6990,22 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="M51" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="N51" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="O51" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="P51" t="n">
         <v>2.1</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.1</v>
+        <v>5</v>
       </c>
       <c r="R51" t="n">
         <v>1.4</v>
@@ -7020,53 +7020,53 @@
         <v>1.36</v>
       </c>
       <c r="V51" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W51" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X51" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="Z51" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AA51" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AD51" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AE51" t="inlineStr">
         <is>
-          <t>['58']</t>
+          <t>['38', '43']</t>
         </is>
       </c>
       <c r="AF51" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['60']</t>
         </is>
       </c>
       <c r="AG51" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AH51" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI51" t="n">
-        <v>1.95</v>
+        <v>1.5</v>
       </c>
       <c r="AJ51" t="n">
-        <v>1.95</v>
+        <v>3</v>
       </c>
       <c r="AK51" s="3" t="n">
         <v>45558.65625</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7108,7 +7108,7 @@
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -7119,65 +7119,65 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.6</v>
+        <v>2.7</v>
       </c>
       <c r="M52" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="N52" t="n">
-        <v>5</v>
+        <v>2.35</v>
       </c>
       <c r="O52" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="P52" t="n">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="Q52" t="n">
-        <v>5.5</v>
+        <v>3</v>
       </c>
       <c r="R52" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="S52" t="n">
-        <v>2.63</v>
+        <v>2.85</v>
       </c>
       <c r="T52" t="n">
-        <v>3</v>
+        <v>2.81</v>
       </c>
       <c r="U52" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="V52" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="W52" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="X52" t="n">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="Z52" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AA52" t="n">
-        <v>3.75</v>
+        <v>3.08</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AC52" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AD52" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
-          <t>['84']</t>
+          <t>['39']</t>
         </is>
       </c>
       <c r="AF52" t="inlineStr">
@@ -7186,16 +7186,16 @@
         </is>
       </c>
       <c r="AG52" t="n">
-        <v>1.18</v>
+        <v>1.48</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.85</v>
+        <v>1.42</v>
       </c>
       <c r="AI52" t="n">
-        <v>1.4</v>
+        <v>2.06</v>
       </c>
       <c r="AJ52" t="n">
-        <v>3.1</v>
+        <v>1.96</v>
       </c>
       <c r="AK52" s="3" t="n">
         <v>45558.65625</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,25 +7222,25 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Morecambe</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H53" t="n">
         <v>2</v>
       </c>
       <c r="I53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -7248,83 +7248,83 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.58</v>
+        <v>1.85</v>
       </c>
       <c r="M53" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="N53" t="n">
-        <v>5.25</v>
+        <v>4.5</v>
       </c>
       <c r="O53" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="P53" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="Q53" t="n">
         <v>5.5</v>
       </c>
       <c r="R53" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="S53" t="n">
-        <v>3</v>
+        <v>2.38</v>
       </c>
       <c r="T53" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V53" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W53" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="X53" t="n">
         <v>2.75</v>
       </c>
-      <c r="U53" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V53" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W53" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X53" t="n">
-        <v>3.35</v>
-      </c>
       <c r="Y53" t="n">
-        <v>1.81</v>
+        <v>2.5</v>
       </c>
       <c r="Z53" t="n">
-        <v>1.91</v>
+        <v>1.53</v>
       </c>
       <c r="AA53" t="n">
-        <v>2.88</v>
+        <v>4.6</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AC53" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="AD53" t="n">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="AE53" t="inlineStr">
         <is>
-          <t>['34', '45+3']</t>
+          <t>['7']</t>
         </is>
       </c>
       <c r="AF53" t="inlineStr">
         <is>
-          <t>['74', '86']</t>
+          <t>['8', '90+3']</t>
         </is>
       </c>
       <c r="AG53" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AH53" t="n">
-        <v>2.32</v>
+        <v>1.96</v>
       </c>
       <c r="AI53" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AJ53" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AK53" s="3" t="n">
         <v>45558.66666666666</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,25 +7351,25 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Morecambe</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H54" t="n">
         <v>2</v>
       </c>
       <c r="I54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -7377,83 +7377,83 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.85</v>
+        <v>1.58</v>
       </c>
       <c r="M54" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="N54" t="n">
-        <v>4.5</v>
+        <v>5.25</v>
       </c>
       <c r="O54" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="P54" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="Q54" t="n">
         <v>5.5</v>
       </c>
       <c r="R54" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="S54" t="n">
-        <v>2.38</v>
+        <v>3</v>
       </c>
       <c r="T54" t="n">
-        <v>3.75</v>
+        <v>2.75</v>
       </c>
       <c r="U54" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="V54" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W54" t="n">
-        <v>1.46</v>
+        <v>1.22</v>
       </c>
       <c r="X54" t="n">
-        <v>2.75</v>
+        <v>3.35</v>
       </c>
       <c r="Y54" t="n">
-        <v>2.5</v>
+        <v>1.81</v>
       </c>
       <c r="Z54" t="n">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="AA54" t="n">
-        <v>4.6</v>
+        <v>2.88</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AC54" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AD54" t="n">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="AE54" t="inlineStr">
         <is>
-          <t>['7']</t>
+          <t>['34', '45+3']</t>
         </is>
       </c>
       <c r="AF54" t="inlineStr">
         <is>
-          <t>['8', '90+3']</t>
+          <t>['74', '86']</t>
         </is>
       </c>
       <c r="AG54" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AH54" t="n">
-        <v>1.96</v>
+        <v>2.32</v>
       </c>
       <c r="AI54" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AJ54" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="AK54" s="3" t="n">
         <v>45558.66666666666</v>
@@ -7599,119 +7599,119 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Boavista FC</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="n">
+        <v>3</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="n">
         <v>2</v>
       </c>
-      <c r="H56" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" t="n">
-        <v>0</v>
-      </c>
       <c r="K56" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.45</v>
+        <v>11</v>
       </c>
       <c r="M56" t="n">
-        <v>4.6</v>
+        <v>5.6</v>
       </c>
       <c r="N56" t="n">
-        <v>5</v>
+        <v>1.23</v>
       </c>
       <c r="O56" t="n">
-        <v>1.91</v>
+        <v>9.5</v>
       </c>
       <c r="P56" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="Q56" t="n">
-        <v>5</v>
+        <v>1.73</v>
       </c>
       <c r="R56" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="S56" t="n">
-        <v>4.45</v>
+        <v>3.25</v>
       </c>
       <c r="T56" t="n">
-        <v>1.92</v>
+        <v>2.5</v>
       </c>
       <c r="U56" t="n">
-        <v>1.88</v>
+        <v>1.5</v>
       </c>
       <c r="V56" t="n">
         <v>1.01</v>
       </c>
       <c r="W56" t="n">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="X56" t="n">
-        <v>7.5</v>
+        <v>3.8</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.33</v>
+        <v>1.95</v>
       </c>
       <c r="Z56" t="n">
-        <v>3</v>
+        <v>1.76</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.75</v>
+        <v>2.88</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.85</v>
+        <v>1.38</v>
       </c>
       <c r="AC56" t="n">
-        <v>1.4</v>
+        <v>2.25</v>
       </c>
       <c r="AD56" t="n">
-        <v>2.75</v>
+        <v>1.57</v>
       </c>
       <c r="AE56" t="inlineStr">
         <is>
-          <t>['55', '90+6']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF56" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['11', '31', '90+1']</t>
         </is>
       </c>
       <c r="AG56" t="n">
-        <v>1.13</v>
+        <v>3.84</v>
       </c>
       <c r="AH56" t="n">
-        <v>2.55</v>
+        <v>1.03</v>
       </c>
       <c r="AI56" t="n">
-        <v>1.42</v>
+        <v>5.5</v>
       </c>
       <c r="AJ56" t="n">
-        <v>2.65</v>
+        <v>1.2</v>
       </c>
       <c r="AK56" s="3" t="n">
         <v>45558.67708333334</v>
@@ -7728,35 +7728,35 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Boavista FC</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H57" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I57" t="n">
         <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -7764,83 +7764,83 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>11</v>
+        <v>1.45</v>
       </c>
       <c r="M57" t="n">
-        <v>5.6</v>
+        <v>4.6</v>
       </c>
       <c r="N57" t="n">
-        <v>1.23</v>
+        <v>5</v>
       </c>
       <c r="O57" t="n">
-        <v>9.5</v>
+        <v>1.91</v>
       </c>
       <c r="P57" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="Q57" t="n">
-        <v>1.73</v>
+        <v>5</v>
       </c>
       <c r="R57" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="S57" t="n">
-        <v>3.25</v>
+        <v>4.45</v>
       </c>
       <c r="T57" t="n">
-        <v>2.5</v>
+        <v>1.92</v>
       </c>
       <c r="U57" t="n">
-        <v>1.5</v>
+        <v>1.88</v>
       </c>
       <c r="V57" t="n">
         <v>1.01</v>
       </c>
       <c r="W57" t="n">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="X57" t="n">
-        <v>3.8</v>
+        <v>7.5</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.95</v>
+        <v>1.33</v>
       </c>
       <c r="Z57" t="n">
-        <v>1.76</v>
+        <v>3</v>
       </c>
       <c r="AA57" t="n">
-        <v>2.88</v>
+        <v>1.75</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.38</v>
+        <v>1.85</v>
       </c>
       <c r="AC57" t="n">
-        <v>2.25</v>
+        <v>1.4</v>
       </c>
       <c r="AD57" t="n">
-        <v>1.57</v>
+        <v>2.75</v>
       </c>
       <c r="AE57" t="inlineStr">
         <is>
+          <t>['55', '90+6']</t>
+        </is>
+      </c>
+      <c r="AF57" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF57" t="inlineStr">
-        <is>
-          <t>['11', '31', '90+1']</t>
-        </is>
-      </c>
       <c r="AG57" t="n">
-        <v>3.84</v>
+        <v>1.13</v>
       </c>
       <c r="AH57" t="n">
-        <v>1.03</v>
+        <v>2.55</v>
       </c>
       <c r="AI57" t="n">
-        <v>5.5</v>
+        <v>1.42</v>
       </c>
       <c r="AJ57" t="n">
-        <v>1.2</v>
+        <v>2.65</v>
       </c>
       <c r="AK57" s="3" t="n">
         <v>45558.67708333334</v>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Paraguay Division Profesional</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,19 +7996,19 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>2 de Mayo</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Sol de América</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I59" t="n">
         <v>0</v>
@@ -8022,83 +8022,83 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.75</v>
+        <v>1.95</v>
       </c>
       <c r="M59" t="n">
         <v>3.1</v>
       </c>
       <c r="N59" t="n">
-        <v>2.7</v>
+        <v>3.8</v>
       </c>
       <c r="O59" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="P59" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="R59" t="n">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="S59" t="n">
-        <v>2.43</v>
+        <v>2.66</v>
       </c>
       <c r="T59" t="n">
-        <v>3.48</v>
+        <v>3.29</v>
       </c>
       <c r="U59" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="V59" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="W59" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="X59" t="n">
-        <v>2.48</v>
+        <v>2.8</v>
       </c>
       <c r="Y59" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="Z59" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE59" t="inlineStr">
+        <is>
+          <t>['51']</t>
+        </is>
+      </c>
+      <c r="AF59" t="inlineStr">
+        <is>
+          <t>['55', '90+4']</t>
+        </is>
+      </c>
+      <c r="AG59" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AH59" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI59" t="n">
         <v>1.62</v>
       </c>
-      <c r="AA59" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AB59" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AC59" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD59" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE59" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF59" t="inlineStr">
-        <is>
-          <t>['64']</t>
-        </is>
-      </c>
-      <c r="AG59" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AH59" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AI59" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AJ59" t="n">
-        <v>1.91</v>
+        <v>2.75</v>
       </c>
       <c r="AK59" s="3" t="n">
         <v>45558.77083333334</v>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Paraguay Division Profesional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,20 +8125,20 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2 de Mayo</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Sol de América</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" t="n">
         <v>1</v>
       </c>
-      <c r="H60" t="n">
-        <v>2</v>
-      </c>
       <c r="I60" t="n">
         <v>0</v>
       </c>
@@ -8151,83 +8151,83 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.95</v>
+        <v>2.75</v>
       </c>
       <c r="M60" t="n">
         <v>3.1</v>
       </c>
       <c r="N60" t="n">
-        <v>3.8</v>
+        <v>2.7</v>
       </c>
       <c r="O60" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="P60" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q60" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="R60" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="S60" t="n">
-        <v>2.66</v>
+        <v>2.43</v>
       </c>
       <c r="T60" t="n">
-        <v>3.29</v>
+        <v>3.48</v>
       </c>
       <c r="U60" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="V60" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="W60" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X60" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AB60" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE60" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF60" t="inlineStr">
+        <is>
+          <t>['64']</t>
+        </is>
+      </c>
+      <c r="AG60" t="n">
         <v>1.37</v>
       </c>
-      <c r="X60" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Y60" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z60" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AA60" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AB60" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC60" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD60" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE60" t="inlineStr">
-        <is>
-          <t>['51']</t>
-        </is>
-      </c>
-      <c r="AF60" t="inlineStr">
-        <is>
-          <t>['55', '90+4']</t>
-        </is>
-      </c>
-      <c r="AG60" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AH60" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AI60" t="n">
-        <v>1.62</v>
+        <v>2.1</v>
       </c>
       <c r="AJ60" t="n">
-        <v>2.75</v>
+        <v>1.91</v>
       </c>
       <c r="AK60" s="3" t="n">
         <v>45558.77083333334</v>
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Banfield</t>
+          <t>Vélez Sarsfield</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Independiente Rivadavia</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,65 +8667,65 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="M64" t="n">
         <v>3.1</v>
       </c>
       <c r="N64" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="O64" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="P64" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="Q64" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="R64" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="S64" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="T64" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="U64" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="V64" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W64" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="X64" t="n">
-        <v>2.35</v>
+        <v>2.6</v>
       </c>
       <c r="Y64" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="Z64" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AA64" t="n">
-        <v>5.05</v>
+        <v>4.8</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AC64" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="AD64" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AE64" t="inlineStr">
         <is>
-          <t>['41', '60']</t>
+          <t>['12', '87']</t>
         </is>
       </c>
       <c r="AF64" t="inlineStr">
@@ -8734,16 +8734,16 @@
         </is>
       </c>
       <c r="AG64" t="n">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="AH64" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AI64" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AJ64" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AK64" s="3" t="n">
         <v>45558.875</v>
@@ -9018,35 +9018,35 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Primera División</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Banfield</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Independiente Rivadavia</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I67" t="n">
         <v>1</v>
       </c>
       <c r="J67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
@@ -9054,83 +9054,83 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="M67" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="N67" t="n">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="O67" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="P67" t="n">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="Q67" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="R67" t="n">
-        <v>1.33</v>
+        <v>1.62</v>
       </c>
       <c r="S67" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="T67" t="n">
-        <v>2.45</v>
+        <v>4</v>
       </c>
       <c r="U67" t="n">
-        <v>1.48</v>
+        <v>1.22</v>
       </c>
       <c r="V67" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="W67" t="n">
-        <v>1.32</v>
+        <v>1.52</v>
       </c>
       <c r="X67" t="n">
-        <v>3.05</v>
+        <v>2.35</v>
       </c>
       <c r="Y67" t="n">
-        <v>1.75</v>
+        <v>2.7</v>
       </c>
       <c r="Z67" t="n">
-        <v>2.05</v>
+        <v>1.44</v>
       </c>
       <c r="AA67" t="n">
-        <v>2.8</v>
+        <v>5.05</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.39</v>
+        <v>1.1</v>
       </c>
       <c r="AC67" t="n">
-        <v>1.73</v>
+        <v>2.38</v>
       </c>
       <c r="AD67" t="n">
-        <v>1.95</v>
+        <v>1.53</v>
       </c>
       <c r="AE67" t="inlineStr">
         <is>
-          <t>['9']</t>
+          <t>['41', '60']</t>
         </is>
       </c>
       <c r="AF67" t="inlineStr">
         <is>
-          <t>['27', '90+4']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG67" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AH67" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="AI67" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AJ67" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="AK67" s="3" t="n">
         <v>45558.875</v>
@@ -9147,35 +9147,35 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Argentina Primera División</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Vélez Sarsfield</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G68" t="n">
+        <v>1</v>
+      </c>
+      <c r="H68" t="n">
         <v>2</v>
-      </c>
-      <c r="H68" t="n">
-        <v>0</v>
       </c>
       <c r="I68" t="n">
         <v>1</v>
       </c>
       <c r="J68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
@@ -9183,83 +9183,83 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="M68" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="N68" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O68" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="P68" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q68" t="n">
         <v>4.5</v>
       </c>
-      <c r="O68" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="P68" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q68" t="n">
-        <v>5</v>
-      </c>
       <c r="R68" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="S68" t="n">
-        <v>2.38</v>
+        <v>3</v>
       </c>
       <c r="T68" t="n">
-        <v>3.5</v>
+        <v>2.45</v>
       </c>
       <c r="U68" t="n">
-        <v>1.29</v>
+        <v>1.48</v>
       </c>
       <c r="V68" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="W68" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="X68" t="n">
-        <v>2.6</v>
+        <v>3.05</v>
       </c>
       <c r="Y68" t="n">
-        <v>2.4</v>
+        <v>1.75</v>
       </c>
       <c r="Z68" t="n">
-        <v>1.53</v>
+        <v>2.05</v>
       </c>
       <c r="AA68" t="n">
-        <v>4.8</v>
+        <v>2.8</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.14</v>
+        <v>1.39</v>
       </c>
       <c r="AC68" t="n">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="AD68" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="AE68" t="inlineStr">
         <is>
-          <t>['12', '87']</t>
+          <t>['9']</t>
         </is>
       </c>
       <c r="AF68" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['27', '90+4']</t>
         </is>
       </c>
       <c r="AG68" t="n">
-        <v>1.24</v>
+        <v>1.13</v>
       </c>
       <c r="AH68" t="n">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="AI68" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AJ68" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="AK68" s="3" t="n">
         <v>45558.875</v>
